--- a/Pruebas calificadas/COLEGIO-BRASILIA-USME-(IED)-1101_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BRASILIA-USME-(IED)-1101_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4333,11 +4277,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4345,7 +4285,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4586,11 +4526,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4598,7 +4534,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4839,11 +4775,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4851,7 +4783,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5092,11 +5024,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5104,7 +5032,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5345,11 +5273,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5357,7 +5281,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5598,11 +5522,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5610,7 +5530,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5851,11 +5771,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5863,7 +5779,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6104,11 +6020,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6116,7 +6028,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6357,11 +6269,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6369,7 +6277,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6610,11 +6518,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6622,7 +6526,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6863,11 +6767,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6875,7 +6775,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7116,11 +7016,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7128,7 +7024,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7369,11 +7265,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7381,7 +7273,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7622,11 +7514,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7634,7 +7522,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7875,11 +7763,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7887,7 +7771,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8128,11 +8012,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8140,7 +8020,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8381,11 +8261,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8393,7 +8269,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8634,11 +8510,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8646,7 +8518,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8887,11 +8759,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8899,7 +8767,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9140,11 +9008,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9152,7 +9016,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9389,11 +9253,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9401,7 +9261,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9642,11 +9502,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9654,7 +9510,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9895,11 +9751,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9907,7 +9759,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10148,11 +10000,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -10160,7 +10008,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10401,11 +10249,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -10413,7 +10257,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10650,11 +10494,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -10662,7 +10502,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10899,11 +10739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -10911,7 +10747,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11152,11 +10988,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -11164,7 +10996,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11405,11 +11237,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -11417,7 +11245,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11654,11 +11482,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -11666,7 +11490,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
